--- a/sample_finance_data.xlsx
+++ b/sample_finance_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\tools\personal\port\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0495C6E4-BBD6-4070-8EBE-3D63B2782842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454E43F-5240-4E29-BF37-4222FD74AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>FundName</t>
   </si>
@@ -133,6 +133,24 @@
   </si>
   <si>
     <t>UTI Nifty 50 Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Motilal Oswal ELSS Tax Saver Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Parag Parikh Flexi Cap Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Navi Nifty Smallcap250 Momentum Quality 100 Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Sundaram Arbitrage Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Nippon India Nifty IT Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>Kotak Nifty Next 50 Index Fund Direct Growth</t>
   </si>
 </sst>
 </file>
@@ -472,10 +490,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -496,10 +514,76 @@
         <v>35</v>
       </c>
       <c r="B2">
-        <v>172.113</v>
+        <v>255.56200000000001</v>
       </c>
       <c r="C2">
         <v>120716</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3">
+        <v>749.70799999999997</v>
+      </c>
+      <c r="C3">
+        <v>148745</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4">
+        <v>3147.7440000000001</v>
+      </c>
+      <c r="C4">
+        <v>153362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>3342.4929999999999</v>
+      </c>
+      <c r="C5">
+        <v>152392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>865.74599999999998</v>
+      </c>
+      <c r="C6">
+        <v>133386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>465.76900000000001</v>
+      </c>
+      <c r="C7">
+        <v>122639</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8">
+        <v>1671.6310000000001</v>
+      </c>
+      <c r="C8">
+        <v>149550</v>
       </c>
     </row>
   </sheetData>
@@ -545,6 +629,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -599,6 +688,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -673,6 +768,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/sample_finance_data.xlsx
+++ b/sample_finance_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\tools\personal\port\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\tools\personal\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454E43F-5240-4E29-BF37-4222FD74AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D1043E-C018-406F-A264-66E2F49DC737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MutualFunds" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,29 @@
     <sheet name="EmergencyFund" sheetId="4" r:id="rId4"/>
     <sheet name="Insurance" sheetId="5" r:id="rId5"/>
     <sheet name="Metals" sheetId="6" r:id="rId6"/>
+    <sheet name="MFTransactions" sheetId="7" r:id="rId7"/>
+    <sheet name="LookThrough" sheetId="8" r:id="rId8"/>
+    <sheet name="Targets" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="258">
   <si>
     <t>FundName</t>
   </si>
@@ -36,6 +52,63 @@
     <t>Identifier</t>
   </si>
   <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>UTI Nifty 50 Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>120716</t>
+  </si>
+  <si>
+    <t>MUTF_IN:UTI_NIFT_50_FGX2CX</t>
+  </si>
+  <si>
+    <t>Kotak Nifty Next 50 Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>148745</t>
+  </si>
+  <si>
+    <t>MUTF_IN:KOTA_NIFT_NEXT_73M1DZ</t>
+  </si>
+  <si>
+    <t>Navi Nifty Smallcap250 Momentum Quality 100 Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>153362</t>
+  </si>
+  <si>
+    <t>MUTF_IN:NAVI_NIFT_SMCP_3JD6FI</t>
+  </si>
+  <si>
+    <t>Nippon India Nifty IT Index Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>152392</t>
+  </si>
+  <si>
+    <t>MUTF_IN:NIPP_INDI_NIFT_L2SD3Y</t>
+  </si>
+  <si>
+    <t>Motilal Oswal ELSS Tax Saver Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>133386</t>
+  </si>
+  <si>
+    <t>MUTF_IN:MOTI_OSWA_ELSS_GGNULV</t>
+  </si>
+  <si>
+    <t>Sundaram Arbitrage Fund Direct Growth</t>
+  </si>
+  <si>
+    <t>149550</t>
+  </si>
+  <si>
+    <t>MUTF_IN:SUND_ARBI_DIR_14G5PYB</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -75,7 +148,7 @@
     <t>RD</t>
   </si>
   <si>
-    <t>2027-04-29</t>
+    <t>2027-09-06</t>
   </si>
   <si>
     <t>HDFC FD</t>
@@ -84,7 +157,7 @@
     <t>FD</t>
   </si>
   <si>
-    <t>2028-04-28</t>
+    <t>2028-09-05</t>
   </si>
   <si>
     <t>Axis Savings</t>
@@ -132,25 +205,616 @@
     <t>Silver</t>
   </si>
   <si>
-    <t>UTI Nifty 50 Index Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Motilal Oswal ELSS Tax Saver Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Parag Parikh Flexi Cap Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Navi Nifty Smallcap250 Momentum Quality 100 Index Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Sundaram Arbitrage Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Nippon India Nifty IT Index Fund Direct Growth</t>
-  </si>
-  <si>
-    <t>Kotak Nifty Next 50 Index Fund Direct Growth</t>
+    <t>FundIdentifier</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>NAV</t>
+  </si>
+  <si>
+    <t>Invested</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>CorporateDebt</t>
+  </si>
+  <si>
+    <t>GovtSecurities</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>AssetClass</t>
+  </si>
+  <si>
+    <t>TargetPct</t>
+  </si>
+  <si>
+    <t>Corporate Debt</t>
+  </si>
+  <si>
+    <t>Government Securities</t>
+  </si>
+  <si>
+    <t>122639</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>28.46</t>
+  </si>
+  <si>
+    <t>87.83</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>93.02</t>
+  </si>
+  <si>
+    <t>59.12</t>
+  </si>
+  <si>
+    <t>2025-07-01</t>
+  </si>
+  <si>
+    <t>57.18</t>
+  </si>
+  <si>
+    <t>92.68</t>
+  </si>
+  <si>
+    <t>89.97</t>
+  </si>
+  <si>
+    <t>61.13</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>57.87</t>
+  </si>
+  <si>
+    <t>91.58</t>
+  </si>
+  <si>
+    <t>92.35</t>
+  </si>
+  <si>
+    <t>59.55</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>95.64</t>
+  </si>
+  <si>
+    <t>57.51</t>
+  </si>
+  <si>
+    <t>57.86</t>
+  </si>
+  <si>
+    <t>91.59</t>
+  </si>
+  <si>
+    <t>168.96</t>
+  </si>
+  <si>
+    <t>15.39</t>
+  </si>
+  <si>
+    <t>308.52</t>
+  </si>
+  <si>
+    <t>9.72</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>320.33</t>
+  </si>
+  <si>
+    <t>9.37</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>169.47</t>
+  </si>
+  <si>
+    <t>15.34</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>150.44</t>
+  </si>
+  <si>
+    <t>59.82</t>
+  </si>
+  <si>
+    <t>21.59</t>
+  </si>
+  <si>
+    <t>92.64</t>
+  </si>
+  <si>
+    <t>546.30</t>
+  </si>
+  <si>
+    <t>9.15</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>168.28</t>
+  </si>
+  <si>
+    <t>15.45</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>32.89</t>
+  </si>
+  <si>
+    <t>60.81</t>
+  </si>
+  <si>
+    <t>105.93</t>
+  </si>
+  <si>
+    <t>94.46</t>
+  </si>
+  <si>
+    <t>167.57</t>
+  </si>
+  <si>
+    <t>15.55</t>
+  </si>
+  <si>
+    <t>206.98</t>
+  </si>
+  <si>
+    <t>9.68</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>101.50</t>
+  </si>
+  <si>
+    <t>9.85</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>66.79</t>
+  </si>
+  <si>
+    <t>59.89</t>
+  </si>
+  <si>
+    <t>84.34</t>
+  </si>
+  <si>
+    <t>94.86</t>
+  </si>
+  <si>
+    <t>196.90</t>
+  </si>
+  <si>
+    <t>10.16</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>25.26</t>
+  </si>
+  <si>
+    <t>59.38</t>
+  </si>
+  <si>
+    <t>166.41</t>
+  </si>
+  <si>
+    <t>15.63</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>43.14</t>
+  </si>
+  <si>
+    <t>57.94</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>34.52</t>
+  </si>
+  <si>
+    <t>57.93</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>34.55</t>
+  </si>
+  <si>
+    <t>57.89</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>34.36</t>
+  </si>
+  <si>
+    <t>58.20</t>
+  </si>
+  <si>
+    <t>52.53</t>
+  </si>
+  <si>
+    <t>95.17</t>
+  </si>
+  <si>
+    <t>165.34</t>
+  </si>
+  <si>
+    <t>15.72</t>
+  </si>
+  <si>
+    <t>291.96</t>
+  </si>
+  <si>
+    <t>10.28</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>146.08</t>
+  </si>
+  <si>
+    <t>20.54</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>895.76</t>
+  </si>
+  <si>
+    <t>11.16</t>
+  </si>
+  <si>
+    <t>537.40</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>164.63</t>
+  </si>
+  <si>
+    <t>15.80</t>
+  </si>
+  <si>
+    <t>150.81</t>
+  </si>
+  <si>
+    <t>19.89</t>
+  </si>
+  <si>
+    <t>284.22</t>
+  </si>
+  <si>
+    <t>10.55</t>
+  </si>
+  <si>
+    <t>381.78</t>
+  </si>
+  <si>
+    <t>10.48</t>
+  </si>
+  <si>
+    <t>50.81</t>
+  </si>
+  <si>
+    <t>177.13</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>163.46</t>
+  </si>
+  <si>
+    <t>15.91</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>40.90</t>
+  </si>
+  <si>
+    <t>171.16</t>
+  </si>
+  <si>
+    <t>153.88</t>
+  </si>
+  <si>
+    <t>19.50</t>
+  </si>
+  <si>
+    <t>362.89</t>
+  </si>
+  <si>
+    <t>8.27</t>
+  </si>
+  <si>
+    <t>495.56</t>
+  </si>
+  <si>
+    <t>10.09</t>
+  </si>
+  <si>
+    <t>14.74</t>
+  </si>
+  <si>
+    <t>169.64</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>6.18</t>
+  </si>
+  <si>
+    <t>161.87</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>337.52</t>
+  </si>
+  <si>
+    <t>16.00</t>
+  </si>
+  <si>
+    <t>Redeemed</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>72.82</t>
+  </si>
+  <si>
+    <t>54.93</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>348.67</t>
+  </si>
+  <si>
+    <t>8.61</t>
+  </si>
+  <si>
+    <t>386.31</t>
+  </si>
+  <si>
+    <t>10.35</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>151.66</t>
+  </si>
+  <si>
+    <t>19.79</t>
+  </si>
+  <si>
+    <t>59.48</t>
+  </si>
+  <si>
+    <t>168.12</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>5.97</t>
+  </si>
+  <si>
+    <t>167.77</t>
+  </si>
+  <si>
+    <t>83.45</t>
+  </si>
+  <si>
+    <t>147.27</t>
+  </si>
+  <si>
+    <t>20.38</t>
+  </si>
+  <si>
+    <t>374.23</t>
+  </si>
+  <si>
+    <t>8.02</t>
+  </si>
+  <si>
+    <t>450.93</t>
+  </si>
+  <si>
+    <t>11.09</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>66.91</t>
+  </si>
+  <si>
+    <t>164.42</t>
+  </si>
+  <si>
+    <t>352.04</t>
+  </si>
+  <si>
+    <t>8.52</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>47.33</t>
+  </si>
+  <si>
+    <t>169.04</t>
+  </si>
+  <si>
+    <t>144.84</t>
+  </si>
+  <si>
+    <t>20.72</t>
+  </si>
+  <si>
+    <t>253.79</t>
+  </si>
+  <si>
+    <t>11.82</t>
+  </si>
+  <si>
+    <t>165.28</t>
+  </si>
+  <si>
+    <t>20.21</t>
+  </si>
+  <si>
+    <t>11.51</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>47.03</t>
+  </si>
+  <si>
+    <t>170.11</t>
+  </si>
+  <si>
+    <t>502.61</t>
+  </si>
+  <si>
+    <t>11.94</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>45.76</t>
+  </si>
+  <si>
+    <t>21.88</t>
+  </si>
+  <si>
+    <t>344.66</t>
+  </si>
+  <si>
+    <t>8.71</t>
+  </si>
+  <si>
+    <t>57.34</t>
+  </si>
+  <si>
+    <t>174.41</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>322.25</t>
+  </si>
+  <si>
+    <t>91.16</t>
+  </si>
+  <si>
+    <t>143.51</t>
+  </si>
+  <si>
+    <t>92.00</t>
+  </si>
+  <si>
+    <t>173.39</t>
+  </si>
+  <si>
+    <t>173.01</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>690.51</t>
+  </si>
+  <si>
+    <t>21.72</t>
+  </si>
+  <si>
+    <t>1522.41</t>
+  </si>
+  <si>
+    <t>16.42</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>405.04</t>
+  </si>
+  <si>
+    <t>12.35</t>
   </si>
 </sst>
 </file>
@@ -490,15 +1154,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="62.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,113 +1172,124 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>255.56200000000001</v>
-      </c>
-      <c r="C2">
-        <v>120716</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>665.68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>749.70799999999997</v>
-      </c>
-      <c r="C3">
-        <v>148745</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1485.98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>3147.7440000000001</v>
-      </c>
-      <c r="C4">
-        <v>153362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4055.4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>3342.4929999999999</v>
-      </c>
-      <c r="C5">
-        <v>152392</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4039.2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>865.74599999999998</v>
-      </c>
-      <c r="C6">
-        <v>133386</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>865.75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B7">
-        <v>465.76900000000001</v>
-      </c>
-      <c r="C7">
-        <v>122639</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8">
-        <v>1671.6310000000001</v>
-      </c>
-      <c r="C8">
-        <v>149550</v>
+        <v>3194.04</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>350000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>180000</v>
@@ -628,52 +1303,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>150000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>50000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>15000</v>
@@ -687,73 +1357,67 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>75000</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>150000</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C4">
         <v>50000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>10000</v>
@@ -767,33 +1431,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C2">
         <v>25000</v>
@@ -802,12 +1461,12 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>18000</v>
@@ -816,12 +1475,12 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>15000</v>
@@ -838,30 +1497,1524 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>161</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E46" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E50" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" t="s">
+        <v>197</v>
+      </c>
+      <c r="E52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>199</v>
+      </c>
+      <c r="E53" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" t="s">
+        <v>209</v>
+      </c>
+      <c r="E57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>214</v>
+      </c>
+      <c r="E60" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" t="s">
+        <v>217</v>
+      </c>
+      <c r="E61" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>216</v>
+      </c>
+      <c r="C62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" t="s">
+        <v>219</v>
+      </c>
+      <c r="E62" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" t="s">
+        <v>222</v>
+      </c>
+      <c r="E63" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" t="s">
+        <v>221</v>
+      </c>
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" t="s">
+        <v>224</v>
+      </c>
+      <c r="E64" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" t="s">
+        <v>192</v>
+      </c>
+      <c r="D66" t="s">
+        <v>222</v>
+      </c>
+      <c r="E66" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" t="s">
+        <v>224</v>
+      </c>
+      <c r="E67" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>59</v>
+      </c>
+      <c r="C68" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" t="s">
+        <v>226</v>
+      </c>
+      <c r="E68" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" t="s">
+        <v>234</v>
+      </c>
+      <c r="E70" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" t="s">
+        <v>236</v>
+      </c>
+      <c r="C71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" t="s">
+        <v>237</v>
+      </c>
+      <c r="E71" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="s">
+        <v>236</v>
+      </c>
+      <c r="C72" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" t="s">
+        <v>239</v>
+      </c>
+      <c r="E72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>236</v>
+      </c>
+      <c r="C73" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" t="s">
+        <v>241</v>
+      </c>
+      <c r="E73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>243</v>
+      </c>
+      <c r="C74" t="s">
+        <v>192</v>
+      </c>
+      <c r="D74" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" t="s">
+        <v>246</v>
+      </c>
+      <c r="E75" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" t="s">
+        <v>250</v>
+      </c>
+      <c r="C77" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" t="s">
+        <v>251</v>
+      </c>
+      <c r="E77" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" t="s">
+        <v>253</v>
+      </c>
+      <c r="E78" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s">
+        <v>255</v>
+      </c>
+      <c r="C79" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" t="s">
+        <v>256</v>
+      </c>
+      <c r="E79" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>255</v>
+      </c>
+      <c r="C80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" t="s">
+        <v>204</v>
+      </c>
+      <c r="E80" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>75</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>68</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
